--- a/12600500.xlsx
+++ b/12600500.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="58">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -1163,25 +1163,47 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="18"/>
-      <c r="B8" s="19"/>
-      <c r="C8" s="19"/>
-      <c r="D8" s="19"/>
-      <c r="E8" s="19"/>
-      <c r="F8" s="19"/>
-      <c r="G8" s="19"/>
-      <c r="H8" s="19"/>
-      <c r="I8" s="20" t="str">
+      <c r="A8" s="18" t="n">
+        <v>46246</v>
+      </c>
+      <c r="B8" s="19" t="n">
+        <v>420</v>
+      </c>
+      <c r="C8" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="D8" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="E8" s="19" t="n">
+        <v>120</v>
+      </c>
+      <c r="F8" s="19" t="n">
+        <v>350</v>
+      </c>
+      <c r="G8" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="H8" s="19" t="n">
+        <v>400</v>
+      </c>
+      <c r="I8" s="20" t="n">
         <f aca="false">IF(SUM(B8:F8,H8)=0,"",SUM(B8:F8,H8))</f>
-        <v/>
-      </c>
-      <c r="J8" s="20" t="str">
+        <v>1380</v>
+      </c>
+      <c r="J8" s="20" t="n">
         <f aca="false">IF(I8="","",1440-I8)</f>
-        <v/>
-      </c>
-      <c r="K8" s="21"/>
-      <c r="L8" s="21"/>
-      <c r="M8" s="21"/>
+        <v>60</v>
+      </c>
+      <c r="K8" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="L8" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="M8" s="21" t="s">
+        <v>54</v>
+      </c>
       <c r="N8" s="22"/>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12600500.xlsx
+++ b/12600500.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="59">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -195,6 +195,9 @@
   </si>
   <si>
     <t xml:space="preserve">feeling tired because of long break between the classes </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unsatisfied</t>
   </si>
 </sst>
 </file>
@@ -1207,25 +1210,47 @@
       <c r="N8" s="22"/>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="18"/>
-      <c r="B9" s="19"/>
-      <c r="C9" s="19"/>
-      <c r="D9" s="19"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="19"/>
-      <c r="G9" s="19"/>
-      <c r="H9" s="19"/>
-      <c r="I9" s="20" t="str">
+      <c r="A9" s="18" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B9" s="19" t="n">
+        <v>540</v>
+      </c>
+      <c r="C9" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="D9" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="E9" s="19" t="n">
+        <v>100</v>
+      </c>
+      <c r="F9" s="19" t="n">
+        <v>100</v>
+      </c>
+      <c r="G9" s="19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H9" s="19" t="n">
+        <v>600</v>
+      </c>
+      <c r="I9" s="20" t="n">
         <f aca="false">IF(SUM(B9:F9,H9)=0,"",SUM(B9:F9,H9))</f>
-        <v/>
-      </c>
-      <c r="J9" s="20" t="str">
+        <v>1430</v>
+      </c>
+      <c r="J9" s="20" t="n">
         <f aca="false">IF(I9="","",1440-I9)</f>
-        <v/>
-      </c>
-      <c r="K9" s="21"/>
-      <c r="L9" s="21"/>
-      <c r="M9" s="21"/>
+        <v>10</v>
+      </c>
+      <c r="K9" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="L9" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="M9" s="21" t="s">
+        <v>56</v>
+      </c>
       <c r="N9" s="22"/>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12600500.xlsx
+++ b/12600500.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="59">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -1254,25 +1254,47 @@
       <c r="N9" s="22"/>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="18"/>
-      <c r="B10" s="19"/>
-      <c r="C10" s="19"/>
-      <c r="D10" s="19"/>
-      <c r="E10" s="19"/>
-      <c r="F10" s="19"/>
-      <c r="G10" s="19"/>
-      <c r="H10" s="19"/>
-      <c r="I10" s="20" t="str">
+      <c r="A10" s="18" t="n">
+        <v>46248</v>
+      </c>
+      <c r="B10" s="19" t="n">
+        <v>420</v>
+      </c>
+      <c r="C10" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="19" t="n">
+        <v>120</v>
+      </c>
+      <c r="E10" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="F10" s="19" t="n">
+        <v>300</v>
+      </c>
+      <c r="G10" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="H10" s="19" t="n">
+        <v>500</v>
+      </c>
+      <c r="I10" s="20" t="n">
         <f aca="false">IF(SUM(B10:F10,H10)=0,"",SUM(B10:F10,H10))</f>
-        <v/>
-      </c>
-      <c r="J10" s="20" t="str">
+        <v>1400</v>
+      </c>
+      <c r="J10" s="20" t="n">
         <f aca="false">IF(I10="","",1440-I10)</f>
-        <v/>
-      </c>
-      <c r="K10" s="21"/>
-      <c r="L10" s="21"/>
-      <c r="M10" s="21"/>
+        <v>40</v>
+      </c>
+      <c r="K10" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="L10" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="M10" s="21" t="s">
+        <v>56</v>
+      </c>
       <c r="N10" s="22"/>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12600500.xlsx
+++ b/12600500.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="61">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -198,6 +198,12 @@
   </si>
   <si>
     <t xml:space="preserve">Unsatisfied</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Good</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High</t>
   </si>
 </sst>
 </file>
@@ -1298,25 +1304,47 @@
       <c r="N10" s="22"/>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="18"/>
-      <c r="B11" s="19"/>
-      <c r="C11" s="19"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="19"/>
-      <c r="G11" s="19"/>
-      <c r="H11" s="19"/>
-      <c r="I11" s="20" t="str">
+      <c r="A11" s="18" t="n">
+        <v>46249</v>
+      </c>
+      <c r="B11" s="19" t="n">
+        <v>600</v>
+      </c>
+      <c r="C11" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="D11" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="19" t="n">
+        <v>800</v>
+      </c>
+      <c r="I11" s="20" t="n">
         <f aca="false">IF(SUM(B11:F11,H11)=0,"",SUM(B11:F11,H11))</f>
-        <v/>
-      </c>
-      <c r="J11" s="20" t="str">
+        <v>1430</v>
+      </c>
+      <c r="J11" s="20" t="n">
         <f aca="false">IF(I11="","",1440-I11)</f>
-        <v/>
-      </c>
-      <c r="K11" s="21"/>
-      <c r="L11" s="21"/>
-      <c r="M11" s="21"/>
+        <v>10</v>
+      </c>
+      <c r="K11" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="L11" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="M11" s="21" t="s">
+        <v>60</v>
+      </c>
       <c r="N11" s="22"/>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12600500.xlsx
+++ b/12600500.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="61">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -1348,25 +1348,47 @@
       <c r="N11" s="22"/>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="18"/>
-      <c r="B12" s="19"/>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="19"/>
-      <c r="G12" s="19"/>
-      <c r="H12" s="19"/>
-      <c r="I12" s="20" t="str">
+      <c r="A12" s="18" t="n">
+        <v>46249</v>
+      </c>
+      <c r="B12" s="19" t="n">
+        <v>600</v>
+      </c>
+      <c r="C12" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="E12" s="19" t="n">
+        <v>120</v>
+      </c>
+      <c r="F12" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="19" t="n">
+        <v>600</v>
+      </c>
+      <c r="I12" s="20" t="n">
         <f aca="false">IF(SUM(B12:F12,H12)=0,"",SUM(B12:F12,H12))</f>
-        <v/>
-      </c>
-      <c r="J12" s="20" t="str">
+        <v>1380</v>
+      </c>
+      <c r="J12" s="20" t="n">
         <f aca="false">IF(I12="","",1440-I12)</f>
-        <v/>
-      </c>
-      <c r="K12" s="21"/>
-      <c r="L12" s="21"/>
-      <c r="M12" s="21"/>
+        <v>60</v>
+      </c>
+      <c r="K12" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="L12" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="M12" s="21" t="s">
+        <v>54</v>
+      </c>
       <c r="N12" s="22"/>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12600500.xlsx
+++ b/12600500.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="61">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -1392,25 +1392,47 @@
       <c r="N12" s="22"/>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="18"/>
-      <c r="B13" s="19"/>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="19"/>
-      <c r="G13" s="19"/>
-      <c r="H13" s="19"/>
-      <c r="I13" s="20" t="str">
+      <c r="A13" s="18" t="n">
+        <v>46249</v>
+      </c>
+      <c r="B13" s="19" t="n">
+        <v>480</v>
+      </c>
+      <c r="C13" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="D13" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="E13" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="19" t="n">
+        <v>420</v>
+      </c>
+      <c r="G13" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="H13" s="19" t="n">
+        <v>400</v>
+      </c>
+      <c r="I13" s="20" t="n">
         <f aca="false">IF(SUM(B13:F13,H13)=0,"",SUM(B13:F13,H13))</f>
-        <v/>
-      </c>
-      <c r="J13" s="20" t="str">
+        <v>1390</v>
+      </c>
+      <c r="J13" s="20" t="n">
         <f aca="false">IF(I13="","",1440-I13)</f>
-        <v/>
-      </c>
-      <c r="K13" s="21"/>
-      <c r="L13" s="21"/>
-      <c r="M13" s="21"/>
+        <v>50</v>
+      </c>
+      <c r="K13" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="L13" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="M13" s="21" t="s">
+        <v>54</v>
+      </c>
       <c r="N13" s="22"/>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12600500.xlsx
+++ b/12600500.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="61">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -1349,7 +1349,7 @@
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="18" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="B12" s="19" t="n">
         <v>600</v>
@@ -1393,7 +1393,7 @@
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="18" t="n">
-        <v>46249</v>
+        <v>46251</v>
       </c>
       <c r="B13" s="19" t="n">
         <v>480</v>
@@ -1436,25 +1436,47 @@
       <c r="N13" s="22"/>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="18"/>
-      <c r="B14" s="19"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="19"/>
-      <c r="G14" s="19"/>
-      <c r="H14" s="19"/>
-      <c r="I14" s="20" t="str">
+      <c r="A14" s="18" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B14" s="19" t="n">
+        <v>420</v>
+      </c>
+      <c r="C14" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="D14" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="E14" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="19" t="n">
+        <v>240</v>
+      </c>
+      <c r="G14" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="H14" s="19" t="n">
+        <v>600</v>
+      </c>
+      <c r="I14" s="20" t="n">
         <f aca="false">IF(SUM(B14:F14,H14)=0,"",SUM(B14:F14,H14))</f>
-        <v/>
-      </c>
-      <c r="J14" s="20" t="str">
+        <v>1350</v>
+      </c>
+      <c r="J14" s="20" t="n">
         <f aca="false">IF(I14="","",1440-I14)</f>
-        <v/>
-      </c>
-      <c r="K14" s="21"/>
-      <c r="L14" s="21"/>
-      <c r="M14" s="21"/>
+        <v>90</v>
+      </c>
+      <c r="K14" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="L14" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="M14" s="21" t="s">
+        <v>54</v>
+      </c>
       <c r="N14" s="22"/>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12600500.xlsx
+++ b/12600500.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="62">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -204,6 +204,9 @@
   </si>
   <si>
     <t xml:space="preserve">High</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Satisfied</t>
   </si>
 </sst>
 </file>
@@ -1480,25 +1483,47 @@
       <c r="N14" s="22"/>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="18"/>
-      <c r="B15" s="19"/>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="19"/>
-      <c r="H15" s="19"/>
-      <c r="I15" s="20" t="str">
+      <c r="A15" s="18" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B15" s="19" t="n">
+        <v>420</v>
+      </c>
+      <c r="C15" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="D15" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="E15" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="F15" s="19" t="n">
+        <v>350</v>
+      </c>
+      <c r="G15" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="H15" s="19" t="n">
+        <v>500</v>
+      </c>
+      <c r="I15" s="20" t="n">
         <f aca="false">IF(SUM(B15:F15,H15)=0,"",SUM(B15:F15,H15))</f>
-        <v/>
-      </c>
-      <c r="J15" s="20" t="str">
+        <v>1420</v>
+      </c>
+      <c r="J15" s="20" t="n">
         <f aca="false">IF(I15="","",1440-I15)</f>
-        <v/>
-      </c>
-      <c r="K15" s="21"/>
-      <c r="L15" s="21"/>
-      <c r="M15" s="21"/>
+        <v>20</v>
+      </c>
+      <c r="K15" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="L15" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="M15" s="21" t="s">
+        <v>60</v>
+      </c>
       <c r="N15" s="22"/>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12600500.xlsx
+++ b/12600500.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="62">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -1527,25 +1527,47 @@
       <c r="N15" s="22"/>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="18"/>
-      <c r="B16" s="19"/>
-      <c r="C16" s="19"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="19"/>
-      <c r="F16" s="19"/>
-      <c r="G16" s="19"/>
-      <c r="H16" s="19"/>
-      <c r="I16" s="20" t="str">
+      <c r="A16" s="18" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B16" s="19" t="n">
+        <v>420</v>
+      </c>
+      <c r="C16" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="D16" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="E16" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="F16" s="19" t="n">
+        <v>100</v>
+      </c>
+      <c r="G16" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="H16" s="19" t="n">
+        <v>700</v>
+      </c>
+      <c r="I16" s="20" t="n">
         <f aca="false">IF(SUM(B16:F16,H16)=0,"",SUM(B16:F16,H16))</f>
-        <v/>
-      </c>
-      <c r="J16" s="20" t="str">
+        <v>1370</v>
+      </c>
+      <c r="J16" s="20" t="n">
         <f aca="false">IF(I16="","",1440-I16)</f>
-        <v/>
-      </c>
-      <c r="K16" s="21"/>
-      <c r="L16" s="21"/>
-      <c r="M16" s="21"/>
+        <v>70</v>
+      </c>
+      <c r="K16" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="L16" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="M16" s="21" t="s">
+        <v>54</v>
+      </c>
       <c r="N16" s="22"/>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12600500.xlsx
+++ b/12600500.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="62">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -1571,25 +1571,47 @@
       <c r="N16" s="22"/>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="18"/>
-      <c r="B17" s="19"/>
-      <c r="C17" s="19"/>
-      <c r="D17" s="19"/>
-      <c r="E17" s="19"/>
-      <c r="F17" s="19"/>
-      <c r="G17" s="19"/>
-      <c r="H17" s="19"/>
-      <c r="I17" s="20" t="str">
+      <c r="A17" s="18" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B17" s="19" t="n">
+        <v>480</v>
+      </c>
+      <c r="C17" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="D17" s="19" t="n">
+        <v>90</v>
+      </c>
+      <c r="E17" s="19" t="n">
+        <v>90</v>
+      </c>
+      <c r="F17" s="19" t="n">
+        <v>300</v>
+      </c>
+      <c r="G17" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="H17" s="19" t="n">
+        <v>400</v>
+      </c>
+      <c r="I17" s="20" t="n">
         <f aca="false">IF(SUM(B17:F17,H17)=0,"",SUM(B17:F17,H17))</f>
-        <v/>
-      </c>
-      <c r="J17" s="20" t="str">
+        <v>1390</v>
+      </c>
+      <c r="J17" s="20" t="n">
         <f aca="false">IF(I17="","",1440-I17)</f>
-        <v/>
-      </c>
-      <c r="K17" s="21"/>
-      <c r="L17" s="21"/>
-      <c r="M17" s="21"/>
+        <v>50</v>
+      </c>
+      <c r="K17" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="L17" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="M17" s="21" t="s">
+        <v>60</v>
+      </c>
       <c r="N17" s="22"/>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12600500.xlsx
+++ b/12600500.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="62">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -1615,25 +1615,47 @@
       <c r="N17" s="22"/>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="18"/>
-      <c r="B18" s="19"/>
-      <c r="C18" s="19"/>
-      <c r="D18" s="19"/>
-      <c r="E18" s="19"/>
-      <c r="F18" s="19"/>
-      <c r="G18" s="19"/>
-      <c r="H18" s="19"/>
-      <c r="I18" s="20" t="str">
+      <c r="A18" s="18" t="n">
+        <v>46256</v>
+      </c>
+      <c r="B18" s="19" t="n">
+        <v>540</v>
+      </c>
+      <c r="C18" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="19" t="n">
+        <v>120</v>
+      </c>
+      <c r="E18" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="F18" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="19" t="n">
+        <v>700</v>
+      </c>
+      <c r="I18" s="20" t="n">
         <f aca="false">IF(SUM(B18:F18,H18)=0,"",SUM(B18:F18,H18))</f>
-        <v/>
-      </c>
-      <c r="J18" s="20" t="str">
+        <v>1420</v>
+      </c>
+      <c r="J18" s="20" t="n">
         <f aca="false">IF(I18="","",1440-I18)</f>
-        <v/>
-      </c>
-      <c r="K18" s="21"/>
-      <c r="L18" s="21"/>
-      <c r="M18" s="21"/>
+        <v>20</v>
+      </c>
+      <c r="K18" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="L18" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="M18" s="21" t="s">
+        <v>54</v>
+      </c>
       <c r="N18" s="22"/>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12600500.xlsx
+++ b/12600500.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="62">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -1659,25 +1659,47 @@
       <c r="N18" s="22"/>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="18"/>
-      <c r="B19" s="19"/>
-      <c r="C19" s="19"/>
-      <c r="D19" s="19"/>
-      <c r="E19" s="19"/>
-      <c r="F19" s="19"/>
-      <c r="G19" s="19"/>
-      <c r="H19" s="19"/>
-      <c r="I19" s="20" t="str">
+      <c r="A19" s="18" t="n">
+        <v>46257</v>
+      </c>
+      <c r="B19" s="19" t="n">
+        <v>540</v>
+      </c>
+      <c r="C19" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="19" t="n">
+        <v>240</v>
+      </c>
+      <c r="E19" s="19" t="n">
+        <v>120</v>
+      </c>
+      <c r="F19" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="19" t="n">
+        <v>500</v>
+      </c>
+      <c r="I19" s="20" t="n">
         <f aca="false">IF(SUM(B19:F19,H19)=0,"",SUM(B19:F19,H19))</f>
-        <v/>
-      </c>
-      <c r="J19" s="20" t="str">
+        <v>1400</v>
+      </c>
+      <c r="J19" s="20" t="n">
         <f aca="false">IF(I19="","",1440-I19)</f>
-        <v/>
-      </c>
-      <c r="K19" s="21"/>
-      <c r="L19" s="21"/>
-      <c r="M19" s="21"/>
+        <v>40</v>
+      </c>
+      <c r="K19" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="L19" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="M19" s="21" t="s">
+        <v>54</v>
+      </c>
       <c r="N19" s="22"/>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12600500.xlsx
+++ b/12600500.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="62">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -1703,25 +1703,47 @@
       <c r="N19" s="22"/>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="18"/>
-      <c r="B20" s="19"/>
-      <c r="C20" s="19"/>
-      <c r="D20" s="19"/>
-      <c r="E20" s="19"/>
-      <c r="F20" s="19"/>
-      <c r="G20" s="19"/>
-      <c r="H20" s="19"/>
-      <c r="I20" s="20" t="str">
+      <c r="A20" s="18" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B20" s="19" t="n">
+        <v>420</v>
+      </c>
+      <c r="C20" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="D20" s="19" t="n">
+        <v>120</v>
+      </c>
+      <c r="E20" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="19" t="n">
+        <v>300</v>
+      </c>
+      <c r="G20" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="H20" s="19" t="n">
+        <v>500</v>
+      </c>
+      <c r="I20" s="20" t="n">
         <f aca="false">IF(SUM(B20:F20,H20)=0,"",SUM(B20:F20,H20))</f>
-        <v/>
-      </c>
-      <c r="J20" s="20" t="str">
+        <v>1370</v>
+      </c>
+      <c r="J20" s="20" t="n">
         <f aca="false">IF(I20="","",1440-I20)</f>
-        <v/>
-      </c>
-      <c r="K20" s="21"/>
-      <c r="L20" s="21"/>
-      <c r="M20" s="21"/>
+        <v>70</v>
+      </c>
+      <c r="K20" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="L20" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="M20" s="21" t="s">
+        <v>54</v>
+      </c>
       <c r="N20" s="22"/>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12600500.xlsx
+++ b/12600500.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="62">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -1587,7 +1587,7 @@
         <v>90</v>
       </c>
       <c r="F17" s="19" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="G17" s="19" t="n">
         <v>5</v>
@@ -1597,11 +1597,11 @@
       </c>
       <c r="I17" s="20" t="n">
         <f aca="false">IF(SUM(B17:F17,H17)=0,"",SUM(B17:F17,H17))</f>
-        <v>1390</v>
+        <v>1340</v>
       </c>
       <c r="J17" s="20" t="n">
         <f aca="false">IF(I17="","",1440-I17)</f>
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K17" s="21" t="s">
         <v>53</v>
@@ -1747,25 +1747,47 @@
       <c r="N20" s="22"/>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="18"/>
-      <c r="B21" s="19"/>
-      <c r="C21" s="19"/>
-      <c r="D21" s="19"/>
-      <c r="E21" s="19"/>
-      <c r="F21" s="19"/>
-      <c r="G21" s="19"/>
-      <c r="H21" s="19"/>
-      <c r="I21" s="20" t="str">
+      <c r="A21" s="18" t="n">
+        <v>46259</v>
+      </c>
+      <c r="B21" s="19" t="n">
+        <v>420</v>
+      </c>
+      <c r="C21" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="19" t="n">
+        <v>120</v>
+      </c>
+      <c r="E21" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="F21" s="19" t="n">
+        <v>350</v>
+      </c>
+      <c r="G21" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="H21" s="19" t="n">
+        <v>450</v>
+      </c>
+      <c r="I21" s="20" t="n">
         <f aca="false">IF(SUM(B21:F21,H21)=0,"",SUM(B21:F21,H21))</f>
-        <v/>
-      </c>
-      <c r="J21" s="20" t="str">
+        <v>1400</v>
+      </c>
+      <c r="J21" s="20" t="n">
         <f aca="false">IF(I21="","",1440-I21)</f>
-        <v/>
-      </c>
-      <c r="K21" s="21"/>
-      <c r="L21" s="21"/>
-      <c r="M21" s="21"/>
+        <v>40</v>
+      </c>
+      <c r="K21" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="L21" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="M21" s="21" t="s">
+        <v>60</v>
+      </c>
       <c r="N21" s="22"/>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12600500.xlsx
+++ b/12600500.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="62">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -1791,25 +1791,47 @@
       <c r="N21" s="22"/>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="18"/>
-      <c r="B22" s="19"/>
-      <c r="C22" s="19"/>
-      <c r="D22" s="19"/>
-      <c r="E22" s="19"/>
-      <c r="F22" s="19"/>
-      <c r="G22" s="19"/>
-      <c r="H22" s="19"/>
-      <c r="I22" s="20" t="str">
+      <c r="A22" s="18" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B22" s="19" t="n">
+        <v>420</v>
+      </c>
+      <c r="C22" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="D22" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="E22" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="F22" s="19" t="n">
+        <v>300</v>
+      </c>
+      <c r="G22" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="H22" s="19" t="n">
+        <v>500</v>
+      </c>
+      <c r="I22" s="20" t="n">
         <f aca="false">IF(SUM(B22:F22,H22)=0,"",SUM(B22:F22,H22))</f>
-        <v/>
-      </c>
-      <c r="J22" s="20" t="str">
+        <v>1370</v>
+      </c>
+      <c r="J22" s="20" t="n">
         <f aca="false">IF(I22="","",1440-I22)</f>
-        <v/>
-      </c>
-      <c r="K22" s="21"/>
-      <c r="L22" s="21"/>
-      <c r="M22" s="21"/>
+        <v>70</v>
+      </c>
+      <c r="K22" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="L22" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="M22" s="21" t="s">
+        <v>54</v>
+      </c>
       <c r="N22" s="22"/>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12600500.xlsx
+++ b/12600500.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="62">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -1835,25 +1835,47 @@
       <c r="N22" s="22"/>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="18"/>
-      <c r="B23" s="19"/>
-      <c r="C23" s="19"/>
-      <c r="D23" s="19"/>
-      <c r="E23" s="19"/>
-      <c r="F23" s="19"/>
-      <c r="G23" s="19"/>
-      <c r="H23" s="19"/>
-      <c r="I23" s="20" t="str">
+      <c r="A23" s="18" t="n">
+        <v>46261</v>
+      </c>
+      <c r="B23" s="19" t="n">
+        <v>420</v>
+      </c>
+      <c r="C23" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="19" t="n">
+        <v>90</v>
+      </c>
+      <c r="E23" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="F23" s="19" t="n">
+        <v>200</v>
+      </c>
+      <c r="G23" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="H23" s="19" t="n">
+        <v>600</v>
+      </c>
+      <c r="I23" s="20" t="n">
         <f aca="false">IF(SUM(B23:F23,H23)=0,"",SUM(B23:F23,H23))</f>
-        <v/>
-      </c>
-      <c r="J23" s="20" t="str">
+        <v>1370</v>
+      </c>
+      <c r="J23" s="20" t="n">
         <f aca="false">IF(I23="","",1440-I23)</f>
-        <v/>
-      </c>
-      <c r="K23" s="21"/>
-      <c r="L23" s="21"/>
-      <c r="M23" s="21"/>
+        <v>70</v>
+      </c>
+      <c r="K23" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="L23" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="M23" s="21" t="s">
+        <v>54</v>
+      </c>
       <c r="N23" s="22"/>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12600500.xlsx
+++ b/12600500.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="62">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -1879,25 +1879,47 @@
       <c r="N23" s="22"/>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="18"/>
-      <c r="B24" s="19"/>
-      <c r="C24" s="19"/>
-      <c r="D24" s="19"/>
-      <c r="E24" s="19"/>
-      <c r="F24" s="19"/>
-      <c r="G24" s="19"/>
-      <c r="H24" s="19"/>
-      <c r="I24" s="20" t="str">
+      <c r="A24" s="18" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B24" s="19" t="n">
+        <v>420</v>
+      </c>
+      <c r="C24" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="D24" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="19" t="n">
+        <v>180</v>
+      </c>
+      <c r="F24" s="19" t="n">
+        <v>200</v>
+      </c>
+      <c r="G24" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="H24" s="19" t="n">
+        <v>600</v>
+      </c>
+      <c r="I24" s="20" t="n">
         <f aca="false">IF(SUM(B24:F24,H24)=0,"",SUM(B24:F24,H24))</f>
-        <v/>
-      </c>
-      <c r="J24" s="20" t="str">
+        <v>1430</v>
+      </c>
+      <c r="J24" s="20" t="n">
         <f aca="false">IF(I24="","",1440-I24)</f>
-        <v/>
-      </c>
-      <c r="K24" s="21"/>
-      <c r="L24" s="21"/>
-      <c r="M24" s="21"/>
+        <v>10</v>
+      </c>
+      <c r="K24" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="L24" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="M24" s="21" t="s">
+        <v>54</v>
+      </c>
       <c r="N24" s="22"/>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12600500.xlsx
+++ b/12600500.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="62">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -1923,25 +1923,47 @@
       <c r="N24" s="22"/>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="18"/>
-      <c r="B25" s="19"/>
-      <c r="C25" s="19"/>
-      <c r="D25" s="19"/>
-      <c r="E25" s="19"/>
-      <c r="F25" s="19"/>
-      <c r="G25" s="19"/>
-      <c r="H25" s="19"/>
-      <c r="I25" s="20" t="str">
+      <c r="A25" s="18" t="n">
+        <v>46263</v>
+      </c>
+      <c r="B25" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="E25" s="19" t="n">
+        <v>1105</v>
+      </c>
+      <c r="F25" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="19" t="n">
+        <v>300</v>
+      </c>
+      <c r="I25" s="20" t="n">
         <f aca="false">IF(SUM(B25:F25,H25)=0,"",SUM(B25:F25,H25))</f>
-        <v/>
-      </c>
-      <c r="J25" s="20" t="str">
+        <v>1435</v>
+      </c>
+      <c r="J25" s="20" t="n">
         <f aca="false">IF(I25="","",1440-I25)</f>
-        <v/>
-      </c>
-      <c r="K25" s="21"/>
-      <c r="L25" s="21"/>
-      <c r="M25" s="21"/>
+        <v>5</v>
+      </c>
+      <c r="K25" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="L25" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="M25" s="21" t="s">
+        <v>54</v>
+      </c>
       <c r="N25" s="22"/>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12600500.xlsx
+++ b/12600500.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="62">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -1967,25 +1967,47 @@
       <c r="N25" s="22"/>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="18"/>
-      <c r="B26" s="19"/>
-      <c r="C26" s="19"/>
-      <c r="D26" s="19"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="19"/>
-      <c r="G26" s="19"/>
-      <c r="H26" s="19"/>
-      <c r="I26" s="20" t="str">
+      <c r="A26" s="18" t="n">
+        <v>46264</v>
+      </c>
+      <c r="B26" s="19" t="n">
+        <v>540</v>
+      </c>
+      <c r="C26" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="19" t="n">
+        <v>900</v>
+      </c>
+      <c r="I26" s="20" t="n">
         <f aca="false">IF(SUM(B26:F26,H26)=0,"",SUM(B26:F26,H26))</f>
-        <v/>
-      </c>
-      <c r="J26" s="20" t="str">
+        <v>1440</v>
+      </c>
+      <c r="J26" s="20" t="n">
         <f aca="false">IF(I26="","",1440-I26)</f>
-        <v/>
-      </c>
-      <c r="K26" s="21"/>
-      <c r="L26" s="21"/>
-      <c r="M26" s="21"/>
+        <v>0</v>
+      </c>
+      <c r="K26" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="L26" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="M26" s="21" t="s">
+        <v>56</v>
+      </c>
       <c r="N26" s="22"/>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12600500.xlsx
+++ b/12600500.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="62">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -2011,25 +2011,47 @@
       <c r="N26" s="22"/>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="18"/>
-      <c r="B27" s="19"/>
-      <c r="C27" s="19"/>
-      <c r="D27" s="19"/>
-      <c r="E27" s="19"/>
-      <c r="F27" s="19"/>
-      <c r="G27" s="19"/>
-      <c r="H27" s="19"/>
-      <c r="I27" s="20" t="str">
+      <c r="A27" s="18" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B27" s="19" t="n">
+        <v>480</v>
+      </c>
+      <c r="C27" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="D27" s="19" t="n">
+        <v>90</v>
+      </c>
+      <c r="E27" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="19" t="n">
+        <v>300</v>
+      </c>
+      <c r="G27" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="H27" s="19" t="n">
+        <v>500</v>
+      </c>
+      <c r="I27" s="20" t="n">
         <f aca="false">IF(SUM(B27:F27,H27)=0,"",SUM(B27:F27,H27))</f>
-        <v/>
-      </c>
-      <c r="J27" s="20" t="str">
+        <v>1400</v>
+      </c>
+      <c r="J27" s="20" t="n">
         <f aca="false">IF(I27="","",1440-I27)</f>
-        <v/>
-      </c>
-      <c r="K27" s="21"/>
-      <c r="L27" s="21"/>
-      <c r="M27" s="21"/>
+        <v>40</v>
+      </c>
+      <c r="K27" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="L27" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="M27" s="21" t="s">
+        <v>54</v>
+      </c>
       <c r="N27" s="22"/>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12600500.xlsx
+++ b/12600500.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="62">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -2055,25 +2055,47 @@
       <c r="N27" s="22"/>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="18"/>
-      <c r="B28" s="19"/>
-      <c r="C28" s="19"/>
-      <c r="D28" s="19"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
-      <c r="G28" s="19"/>
-      <c r="H28" s="19"/>
-      <c r="I28" s="20" t="str">
+      <c r="A28" s="18" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B28" s="19" t="n">
+        <v>420</v>
+      </c>
+      <c r="C28" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="E28" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="19" t="n">
+        <v>350</v>
+      </c>
+      <c r="G28" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="H28" s="19" t="n">
+        <v>600</v>
+      </c>
+      <c r="I28" s="20" t="n">
         <f aca="false">IF(SUM(B28:F28,H28)=0,"",SUM(B28:F28,H28))</f>
-        <v/>
-      </c>
-      <c r="J28" s="20" t="str">
+        <v>1430</v>
+      </c>
+      <c r="J28" s="20" t="n">
         <f aca="false">IF(I28="","",1440-I28)</f>
-        <v/>
-      </c>
-      <c r="K28" s="21"/>
-      <c r="L28" s="21"/>
-      <c r="M28" s="21"/>
+        <v>10</v>
+      </c>
+      <c r="K28" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="L28" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="M28" s="21" t="s">
+        <v>54</v>
+      </c>
       <c r="N28" s="22"/>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12600500.xlsx
+++ b/12600500.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="62">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -2099,25 +2099,47 @@
       <c r="N28" s="22"/>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="18"/>
-      <c r="B29" s="19"/>
-      <c r="C29" s="19"/>
-      <c r="D29" s="19"/>
-      <c r="E29" s="19"/>
-      <c r="F29" s="19"/>
-      <c r="G29" s="19"/>
-      <c r="H29" s="19"/>
-      <c r="I29" s="20" t="str">
+      <c r="A29" s="18" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B29" s="19" t="n">
+        <v>420</v>
+      </c>
+      <c r="C29" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="19" t="n">
+        <v>100</v>
+      </c>
+      <c r="E29" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="F29" s="19" t="n">
+        <v>300</v>
+      </c>
+      <c r="G29" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="H29" s="19" t="n">
+        <v>550</v>
+      </c>
+      <c r="I29" s="20" t="n">
         <f aca="false">IF(SUM(B29:F29,H29)=0,"",SUM(B29:F29,H29))</f>
-        <v/>
-      </c>
-      <c r="J29" s="20" t="str">
+        <v>1430</v>
+      </c>
+      <c r="J29" s="20" t="n">
         <f aca="false">IF(I29="","",1440-I29)</f>
-        <v/>
-      </c>
-      <c r="K29" s="21"/>
-      <c r="L29" s="21"/>
-      <c r="M29" s="21"/>
+        <v>10</v>
+      </c>
+      <c r="K29" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="L29" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="M29" s="21" t="s">
+        <v>60</v>
+      </c>
       <c r="N29" s="22"/>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12600500.xlsx
+++ b/12600500.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="62">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -2143,25 +2143,47 @@
       <c r="N29" s="22"/>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="18"/>
-      <c r="B30" s="19"/>
-      <c r="C30" s="19"/>
-      <c r="D30" s="19"/>
-      <c r="E30" s="19"/>
-      <c r="F30" s="19"/>
-      <c r="G30" s="19"/>
-      <c r="H30" s="19"/>
-      <c r="I30" s="20" t="str">
+      <c r="A30" s="18" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B30" s="19" t="n">
+        <v>420</v>
+      </c>
+      <c r="C30" s="19" t="n">
+        <v>15</v>
+      </c>
+      <c r="D30" s="19" t="n">
+        <v>120</v>
+      </c>
+      <c r="E30" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="F30" s="19" t="n">
+        <v>150</v>
+      </c>
+      <c r="G30" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H30" s="19" t="n">
+        <v>650</v>
+      </c>
+      <c r="I30" s="20" t="n">
         <f aca="false">IF(SUM(B30:F30,H30)=0,"",SUM(B30:F30,H30))</f>
-        <v/>
-      </c>
-      <c r="J30" s="20" t="str">
+        <v>1415</v>
+      </c>
+      <c r="J30" s="20" t="n">
         <f aca="false">IF(I30="","",1440-I30)</f>
-        <v/>
-      </c>
-      <c r="K30" s="21"/>
-      <c r="L30" s="21"/>
-      <c r="M30" s="21"/>
+        <v>25</v>
+      </c>
+      <c r="K30" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="L30" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="M30" s="21" t="s">
+        <v>60</v>
+      </c>
       <c r="N30" s="22"/>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12600500.xlsx
+++ b/12600500.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="62">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -2187,25 +2187,47 @@
       <c r="N30" s="22"/>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="18"/>
-      <c r="B31" s="19"/>
-      <c r="C31" s="19"/>
-      <c r="D31" s="19"/>
-      <c r="E31" s="19"/>
-      <c r="F31" s="19"/>
-      <c r="G31" s="19"/>
-      <c r="H31" s="19"/>
-      <c r="I31" s="20" t="str">
+      <c r="A31" s="18" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B31" s="19" t="n">
+        <v>420</v>
+      </c>
+      <c r="C31" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="E31" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="19" t="n">
+        <v>200</v>
+      </c>
+      <c r="G31" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="H31" s="19" t="n">
+        <v>700</v>
+      </c>
+      <c r="I31" s="20" t="n">
         <f aca="false">IF(SUM(B31:F31,H31)=0,"",SUM(B31:F31,H31))</f>
-        <v/>
-      </c>
-      <c r="J31" s="20" t="str">
+        <v>1380</v>
+      </c>
+      <c r="J31" s="20" t="n">
         <f aca="false">IF(I31="","",1440-I31)</f>
-        <v/>
-      </c>
-      <c r="K31" s="21"/>
-      <c r="L31" s="21"/>
-      <c r="M31" s="21"/>
+        <v>60</v>
+      </c>
+      <c r="K31" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="L31" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="M31" s="21" t="s">
+        <v>60</v>
+      </c>
       <c r="N31" s="22"/>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/12600500.xlsx
+++ b/12600500.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="62">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -2206,7 +2206,7 @@
         <v>200</v>
       </c>
       <c r="G31" s="19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H31" s="19" t="n">
         <v>700</v>
@@ -2231,25 +2231,47 @@
       <c r="N31" s="22"/>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="18"/>
-      <c r="B32" s="19"/>
-      <c r="C32" s="19"/>
-      <c r="D32" s="19"/>
-      <c r="E32" s="19"/>
-      <c r="F32" s="19"/>
-      <c r="G32" s="19"/>
-      <c r="H32" s="19"/>
-      <c r="I32" s="20" t="str">
+      <c r="A32" s="18" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B32" s="19" t="n">
+        <v>540</v>
+      </c>
+      <c r="C32" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="E32" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="19" t="n">
+        <v>800</v>
+      </c>
+      <c r="I32" s="20" t="n">
         <f aca="false">IF(SUM(B32:F32,H32)=0,"",SUM(B32:F32,H32))</f>
-        <v/>
-      </c>
-      <c r="J32" s="20" t="str">
+        <v>1400</v>
+      </c>
+      <c r="J32" s="20" t="n">
         <f aca="false">IF(I32="","",1440-I32)</f>
-        <v/>
-      </c>
-      <c r="K32" s="21"/>
-      <c r="L32" s="21"/>
-      <c r="M32" s="21"/>
+        <v>40</v>
+      </c>
+      <c r="K32" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="L32" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="M32" s="21" t="s">
+        <v>56</v>
+      </c>
       <c r="N32" s="22"/>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
